--- a/data/objects.xlsx
+++ b/data/objects.xlsx
@@ -449,12 +449,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>V-200</t>
+          <t>V-100</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Юг → Автовокзал → Центр → Ижевский пруд</t>
+          <t>Север → Лента → Столица → Юг</t>
         </is>
       </c>
     </row>
@@ -469,12 +469,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>V-100</t>
+          <t>V-400</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Столица → Центр → Запад → Автовокзал</t>
+          <t>Центр → Ижмаш → Лента → Аэропорт</t>
         </is>
       </c>
     </row>
@@ -489,12 +489,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>V-300</t>
+          <t>V-200</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ижевский пруд → Парк Кирова → Центр → Аэропорт</t>
+          <t>Автовокзал → Юг → Запад → УдГУ</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Металлург → Север → Ижмаш → Парк Кирова</t>
+          <t>Лента → Север → Металлург → Центр</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Лента → Ижевский пруд → Парк Кирова → УдГУ</t>
+          <t>УдГУ → Центр → Лента</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Восток → Столица → Зоопарк → Запад</t>
+          <t>Столица → Центр → Запад → Автовокзал</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Центр → Ижмаш → Лента → Аэропорт</t>
+          <t>Ижевский пруд → Парк Кирова → Центр → Аэропорт</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Зоопарк → Центр → Восток → Лента</t>
+          <t>Запад → Зоопарк → Парк Кирова → Север</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Запад → Зоопарк → Парк Кирова → Север</t>
+          <t>УдГУ → Зоопарк → Восток → Аэропорт</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Аэропорт → Юг → УдГУ → Парк Кирова</t>
+          <t>Автовокзал → УдГУ → Парк Кирова → Ижевский пруд</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Парк Кирова → Ижмаш → Столица → Автовокзал</t>
+          <t>Север → Металлург → Центр → Юг</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Север → Металлург → Центр → Юг</t>
+          <t>Зоопарк → Центр → Восток → Лента</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>УдГУ → Зоопарк → Восток → Аэропорт</t>
+          <t>Юг → Автовокзал → Центр → Ижевский пруд</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Аэропорт → Восток → Лента → Центр</t>
+          <t>Парк Кирова → Ижмаш → Столица → Автовокзал</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Лента → Север → Металлург → Центр</t>
+          <t>Металлург → Север → Ижмаш → Парк Кирова</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Автовокзал → УдГУ → Парк Кирова → Ижевский пруд</t>
+          <t>Аэропорт → Восток → Лента → Центр</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Запад → УдГУ → Столица → Восток</t>
+          <t>Лента → Ижевский пруд → Парк Кирова → УдГУ</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Север → Лента → Столица → Юг</t>
+          <t>Восток → Столица → Зоопарк → Запад</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>УдГУ → Центр → Лента</t>
+          <t>Запад → УдГУ → Столица → Восток</t>
         </is>
       </c>
     </row>
